--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>TESTSHP584</t>
+  </si>
+  <si>
+    <t>TESTSHP798</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -543,6 +546,11 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>TESTSHP798</t>
+  </si>
+  <si>
+    <t>TESTSHP380</t>
   </si>
 </sst>
 </file>
@@ -440,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -551,6 +554,16 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>TESTSHP380</t>
+  </si>
+  <si>
+    <t>TESTSHP127</t>
   </si>
 </sst>
 </file>
@@ -443,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -564,6 +567,11 @@
         <v>21</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>TESTSHP127</t>
+  </si>
+  <si>
+    <t>TESTSHP245</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -572,6 +575,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>TESTSHP245</t>
+  </si>
+  <si>
+    <t>TESTSHP526</t>
+  </si>
+  <si>
+    <t>TESTSHP240</t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -580,6 +586,16 @@
         <v>23</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/OTM Shipment data.xlsx
+++ b/Data Files/OTM Test Data/OTM Shipment data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Shipment IDs</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>TESTSHP240</t>
+  </si>
+  <si>
+    <t>TESTSHP508</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5914F58-C128-4014-8211-4318376D208D}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.359375" collapsed="true"/>
@@ -596,6 +599,16 @@
         <v>25</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
